--- a/AAII_Financials/Yearly/TLGPY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TLGPY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="92">
   <si>
     <t>TLGPY</t>
   </si>
@@ -656,171 +656,183 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44742</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44377</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44012</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43646</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43281</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42916</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42551</v>
       </c>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>15867900</v>
+      </c>
+      <c r="E8" s="3">
         <v>15161000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>15297600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>15109500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>14659600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>16162800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>16369800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>17710700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>19118300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>17332500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>17145300</v>
       </c>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>7919100</v>
+      </c>
+      <c r="E9" s="3">
         <v>7917800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>8269300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>8243600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>8106000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>9053100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>8978200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>9652900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>9976300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>5111200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4795300</v>
       </c>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>7948800</v>
+      </c>
+      <c r="E10" s="3">
         <v>7243200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>7028300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>6865900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>6553700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>7109800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>7391600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>8057800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>9142000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>12221300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>12350000</v>
       </c>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -835,8 +847,9 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -870,9 +883,12 @@
       <c r="M12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O12" s="3"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -906,81 +922,90 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>192300</v>
+      </c>
+      <c r="E14" s="3">
         <v>111500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>481100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-30000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-186000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-746000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-1365600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-682200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-1431200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>363800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>294500</v>
       </c>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3347600</v>
+      </c>
+      <c r="E15" s="3">
         <v>3075500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2988400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2975000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>3002600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3483300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>3685400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3002400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3306200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2959000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2749400</v>
       </c>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -992,80 +1017,87 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>12958800</v>
+      </c>
+      <c r="E17" s="3">
         <v>12498500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>12811600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>12891800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>12858600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>14691900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>15143600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>15835100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>16335800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>14637900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>13721700</v>
       </c>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2909000</v>
+      </c>
+      <c r="E18" s="3">
         <v>2662400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2486000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2217600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1801000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1471000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1226200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1875600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2782500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2694500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3423600</v>
       </c>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1080,188 +1112,204 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-43600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-26900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-26000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>3300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-27600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-6000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>175400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-54700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-51800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1560500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>818500</v>
       </c>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3"/>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>6300200</v>
+      </c>
+      <c r="E21" s="3">
         <v>5764800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>5500400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>5189400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>4831200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>4960300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>4736300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>4932700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>6140500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>7190500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>7015600</v>
       </c>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>523000</v>
+      </c>
+      <c r="E22" s="3">
         <v>489700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>451700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>398000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>321100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>409400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>504000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>481700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>500000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>492400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>536600</v>
       </c>
-      <c r="N22" s="3"/>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3"/>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2292600</v>
+      </c>
+      <c r="E23" s="3">
         <v>2148400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1644600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1905500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1709400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1830100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1930400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2154000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3801000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3762600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3705500</v>
       </c>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>628200</v>
+      </c>
+      <c r="E24" s="3">
         <v>612300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>451700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>540400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>459600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>404100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>660700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>647200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1170100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1181300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1169900</v>
       </c>
-      <c r="N24" s="3"/>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1295,81 +1343,90 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3"/>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1664500</v>
+      </c>
+      <c r="E26" s="3">
         <v>1536100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1193000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1365100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1249800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1426000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1269700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1506800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2630900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2581200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2535600</v>
       </c>
-      <c r="N26" s="3"/>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3"/>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1550300</v>
+      </c>
+      <c r="E27" s="3">
         <v>1424000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1082200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1283200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1163000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1392300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1255900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1510300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2656100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2592600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2490000</v>
       </c>
-      <c r="N27" s="3"/>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3"/>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1403,9 +1460,12 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-      <c r="N28" s="3"/>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3"/>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1437,11 +1497,14 @@
         <v>0</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>1334600</v>
       </c>
-      <c r="N29" s="3"/>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3"/>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1475,9 +1538,12 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-      <c r="N30" s="3"/>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3"/>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1511,81 +1577,90 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-      <c r="N31" s="3"/>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3"/>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>43600</v>
+      </c>
+      <c r="E32" s="3">
         <v>26900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>26000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-3300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>27600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>6000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-175400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>54700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>51800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1560500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-818500</v>
       </c>
-      <c r="N32" s="3"/>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3"/>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1550300</v>
+      </c>
+      <c r="E33" s="3">
         <v>1424000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1082200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1283200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1163000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1392300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1255900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1510300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2656100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2592600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3824600</v>
       </c>
-      <c r="N33" s="3"/>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1619,86 +1694,95 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-      <c r="N34" s="3"/>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1550300</v>
+      </c>
+      <c r="E35" s="3">
         <v>1424000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1082200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1283200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1163000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1392300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1255900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1510300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2656100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2592600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3824600</v>
       </c>
-      <c r="N35" s="3"/>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44742</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44377</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44012</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43646</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43281</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42916</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42551</v>
       </c>
-      <c r="N38" s="2"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O38" s="2"/>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1713,8 +1797,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1729,332 +1814,360 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>763100</v>
+      </c>
+      <c r="E41" s="3">
         <v>663500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>697900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>620300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>716500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>843500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>344500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>423500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>465200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1250000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2349000</v>
       </c>
-      <c r="N41" s="3"/>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3"/>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>51200</v>
+      </c>
+      <c r="E42" s="3">
         <v>3300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>18000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>15300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>5500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>31500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>12400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>30200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2200</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
-      <c r="N42" s="3"/>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2414400</v>
+      </c>
+      <c r="E43" s="3">
         <v>2572000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2577400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2907200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2818700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3435300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3537000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3785600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4137600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7708400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3139800</v>
       </c>
-      <c r="N43" s="3"/>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3"/>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>356300</v>
+      </c>
+      <c r="E44" s="3">
         <v>318000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>345600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>363400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>328000</v>
-      </c>
-      <c r="H44" s="3">
-        <v>288600</v>
       </c>
       <c r="I44" s="3">
         <v>288600</v>
       </c>
       <c r="J44" s="3">
+        <v>288600</v>
+      </c>
+      <c r="K44" s="3">
         <v>314100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>363900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>907500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>368600</v>
       </c>
-      <c r="N44" s="3"/>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3"/>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>411600</v>
+      </c>
+      <c r="E45" s="3">
         <v>474000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>230200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>356700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>282500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>521100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>145700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>246800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>104300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>359100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>322900</v>
       </c>
-      <c r="N45" s="3"/>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4280200</v>
+      </c>
+      <c r="E46" s="3">
         <v>4258200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4074600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4481200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4313100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5333600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4511200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5120600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5392000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5361700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6180300</v>
       </c>
-      <c r="N46" s="3"/>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="3"/>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>441400</v>
+      </c>
+      <c r="E47" s="3">
         <v>395300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>446400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>471200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>589100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>818000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>792600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1169500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1263300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1663100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1229400</v>
       </c>
-      <c r="N47" s="3"/>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3"/>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>16161900</v>
+      </c>
+      <c r="E48" s="3">
         <v>15296700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>15701200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>15836300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>16129900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>17780000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>16935200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>15310600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>16352100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>28451000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>13618400</v>
       </c>
-      <c r="N48" s="3"/>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3"/>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>7499800</v>
+      </c>
+      <c r="E49" s="3">
         <v>7719800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8287300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>7313800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5618700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5346400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5117400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5403200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5859500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>11910100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>6106800</v>
       </c>
-      <c r="N49" s="3"/>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3"/>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2088,9 +2201,12 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-      <c r="N50" s="3"/>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3"/>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2124,45 +2240,51 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-      <c r="N51" s="3"/>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3"/>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>515400</v>
+      </c>
+      <c r="E52" s="3">
         <v>537600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>533800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>541100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>666300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>775200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1350500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1417800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1302500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1889000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1507400</v>
       </c>
-      <c r="N52" s="3"/>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3"/>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2196,45 +2318,51 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-      <c r="N53" s="3"/>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3"/>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>30521600</v>
+      </c>
+      <c r="E54" s="3">
         <v>29481400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>30391000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>29969400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>28681300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>31882600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>30656600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>29861900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>31599900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>27988600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>28642300</v>
       </c>
-      <c r="N54" s="3"/>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O54" s="3"/>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2249,8 +2377,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2265,224 +2394,243 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>864100</v>
+      </c>
+      <c r="E57" s="3">
         <v>732300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>984800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1058900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>907400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>902700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>682100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>595300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1174600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3417500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>969400</v>
       </c>
-      <c r="N57" s="3"/>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3"/>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2680000</v>
+      </c>
+      <c r="E58" s="3">
         <v>3181700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2877600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2073200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2191000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3118900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2366700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1598000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1210100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3299500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1756800</v>
       </c>
-      <c r="N58" s="3"/>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3"/>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1865100</v>
+      </c>
+      <c r="E59" s="3">
         <v>1825900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2001600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1908800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1732800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1851900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2040900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2237400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1883900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4598100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3353500</v>
       </c>
-      <c r="N59" s="3"/>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3"/>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7189200</v>
+      </c>
+      <c r="E60" s="3">
         <v>7553300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7690200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6716800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6681800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7815300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6969100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6698200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6497800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6050700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6079700</v>
       </c>
-      <c r="N60" s="3"/>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O60" s="3"/>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>10411600</v>
+      </c>
+      <c r="E61" s="3">
         <v>8699900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>8617600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>8491200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7850400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>10224900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>11097100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>10737600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>11615400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>9866600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>9691900</v>
       </c>
-      <c r="N61" s="3"/>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3"/>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>214500</v>
+      </c>
+      <c r="E62" s="3">
         <v>160600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>137400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>386700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>242500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>101200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>101500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>158500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>172300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3416100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2345100</v>
       </c>
-      <c r="N62" s="3"/>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3"/>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2516,9 +2664,12 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-      <c r="N63" s="3"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3"/>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2552,9 +2703,12 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-      <c r="N64" s="3"/>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3"/>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2588,45 +2742,51 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-      <c r="N65" s="3"/>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3"/>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>20154300</v>
+      </c>
+      <c r="E66" s="3">
         <v>18784500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>18813700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>18111800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>16985000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>20430300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>20198800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>19674000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>20787000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>18572400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>18140500</v>
       </c>
-      <c r="N66" s="3"/>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O66" s="3"/>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2641,8 +2801,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2676,9 +2837,12 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-      <c r="N68" s="3"/>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3"/>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2712,9 +2876,12 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-      <c r="N69" s="3"/>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3"/>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2748,9 +2915,12 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-      <c r="N70" s="3"/>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3"/>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2784,45 +2954,51 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-      <c r="N71" s="3"/>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3"/>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>8195100</v>
+      </c>
+      <c r="E72" s="3">
         <v>7750600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7832300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>8115100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>8360200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7502600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>6911100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7118900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7639100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>6467800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7040500</v>
       </c>
-      <c r="N72" s="3"/>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3"/>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2856,9 +3032,12 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-      <c r="N73" s="3"/>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3"/>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2892,9 +3071,12 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-      <c r="N74" s="3"/>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3"/>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2928,45 +3110,51 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-      <c r="N75" s="3"/>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3"/>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8702900</v>
+      </c>
+      <c r="E76" s="3">
         <v>9112300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9956000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>10254200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>10671100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>10937200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9992400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>10201200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>10822500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>9416200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>10501800</v>
       </c>
-      <c r="N76" s="3"/>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O76" s="3"/>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3000,86 +3188,95 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-      <c r="N77" s="3"/>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3"/>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44742</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44377</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44012</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43646</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43281</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42916</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42551</v>
       </c>
-      <c r="N80" s="2"/>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O80" s="2"/>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1550300</v>
+      </c>
+      <c r="E81" s="3">
         <v>1424000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1082200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1283200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1163000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1392300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1255900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1510300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2656100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2592600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3824600</v>
       </c>
-      <c r="N81" s="3"/>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3"/>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3094,44 +3291,48 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2107900</v>
+      </c>
+      <c r="E83" s="3">
         <v>1976000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2033600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1995300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2176500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2498100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2605600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1922600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2222600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2959000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2756000</v>
       </c>
-      <c r="N83" s="3"/>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3"/>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3165,9 +3366,12 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-      <c r="N84" s="3"/>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3"/>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3201,9 +3405,12 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-      <c r="N85" s="3"/>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3"/>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3237,9 +3444,12 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-      <c r="N86" s="3"/>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3"/>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3273,9 +3483,12 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-      <c r="N87" s="3"/>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3"/>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3309,45 +3522,51 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-      <c r="N88" s="3"/>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3"/>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5225900</v>
+      </c>
+      <c r="E89" s="3">
         <v>4801700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4703100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4527100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4994500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>5421400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4839800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>4685900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>6365400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>5180500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>5381600</v>
       </c>
-      <c r="N89" s="3"/>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3"/>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3362,44 +3581,48 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1804900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1557100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1526600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1646600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1499200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1558700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1616300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2248600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2641300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2482000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2018800</v>
       </c>
-      <c r="N91" s="3"/>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3"/>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3433,9 +3656,12 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-      <c r="N92" s="3"/>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3"/>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3469,45 +3695,51 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-      <c r="N93" s="3"/>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3"/>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2402600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2208100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3329300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3960700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2339100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1757400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2054700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2534700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2892800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2851100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1460400</v>
       </c>
-      <c r="N94" s="3"/>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3"/>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3522,44 +3754,48 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1564900</v>
+      </c>
+      <c r="E96" s="3">
         <v>1401000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>1349100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>1307200</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>1300800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>891400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>820900</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>1583900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>2329900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-2489300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-2505900</v>
       </c>
-      <c r="N96" s="3"/>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3"/>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3593,9 +3829,12 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-      <c r="N97" s="3"/>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3"/>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3629,9 +3868,12 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-      <c r="N98" s="3"/>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3"/>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3665,115 +3907,127 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-      <c r="N99" s="3"/>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3"/>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2732600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2620500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1295700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-644900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2736000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-3175900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2856900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2165200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3709300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-4067100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2499200</v>
       </c>
-      <c r="N100" s="3"/>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3"/>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-27700</v>
+      </c>
+      <c r="E101" s="3">
         <v>4600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-2000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>6700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>22000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-18700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>2800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>3000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-4000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>3300</v>
       </c>
-      <c r="N101" s="3"/>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3"/>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>63000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-22300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>76100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-71900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-58600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>469300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-72500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-11200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-233700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1741700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1425300</v>
       </c>
-      <c r="N102" s="3"/>
+      <c r="O102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
